--- a/assets/standards/ISO/screw/ISO Standards - ISO 898-1.xlsx
+++ b/assets/standards/ISO/screw/ISO Standards - ISO 898-1.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Table 4" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Table 5" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Table 6" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Table 7" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Table 3" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Table 4" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Table 5" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Table 6" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Table 7" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="/0dmiLE3j+xp3W+i4lRKIeaDUE47HHIfeHoeP3/CKnI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="/x6+Nn6UsJ8pSQyeu/ne7J0c9hnm4/PrEN1Biz8qBMo="/>
     </ext>
   </extLst>
 </workbook>
@@ -27,7 +28,7 @@
     <comment authorId="0" ref="C15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQc
+ID#AAACGNTNROA
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -35,7 +36,7 @@
     <comment authorId="0" ref="C14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQU
+ID#AAACGNTNRN0
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -43,7 +44,7 @@
     <comment authorId="0" ref="E15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpARE
+ID#AAACGNTNROU
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -51,15 +52,7 @@
     <comment authorId="0" ref="H18">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQk
-Unknown Author    (2026-08-28 14:11:25)
-d  For structural bolting: 70 000 N (for M12), 95 500 N (for M14) and 130 000 N (for M16), instead of the table value in the 8.8 column.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="H17">
-      <text>
-        <t xml:space="preserve">======
-ID#AAACGKLpARQ
+ID#AAACGNTNROE
 Unknown Author    (2026-08-28 14:11:25)
 d  For structural bolting: 70 000 N (for M12), 95 500 N (for M14) and 130 000 N (for M16), instead of the table value in the 8.8 column.</t>
       </text>
@@ -67,15 +60,23 @@
     <comment authorId="0" ref="E14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQs
+ID#AAACGNTNRN4
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="H17">
+      <text>
+        <t xml:space="preserve">======
+ID#AAACGNTNROo
+Unknown Author    (2026-08-28 14:11:25)
+d  For structural bolting: 70 000 N (for M12), 95 500 N (for M14) and 130 000 N (for M16), instead of the table value in the 8.8 column.</t>
       </text>
     </comment>
     <comment authorId="0" ref="H16">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQY
+ID#AAACGNTNRN8
 Unknown Author    (2026-08-28 14:11:25)
 d  For structural bolting: 70 000 N (for M12), 95 500 N (for M14) and 130 000 N (for M16), instead of the table value in the 8.8 column.</t>
       </text>
@@ -83,7 +84,7 @@
     <comment authorId="0" ref="H15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpARM
+ID#AAACGNTNROs
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -91,7 +92,7 @@
     <comment authorId="0" ref="H14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQ0
+ID#AAACGNTNROY
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -99,7 +100,7 @@
     <comment authorId="0" ref="J15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQE
+ID#AAACGNTNROg
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -107,7 +108,7 @@
     <comment authorId="0" ref="J14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpARA
+ID#AAACGNURQgY
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -115,7 +116,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgGZIIDBq6zA/Hfqm1NLL8+eV45MQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhBbNGxqQ3POkC8JJ84CFKgzHTMiw=="/>
     </ext>
   </extLst>
 </comments>
@@ -130,7 +131,7 @@
     <comment authorId="0" ref="C15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQA
+ID#AAACGNURQgw
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -138,7 +139,7 @@
     <comment authorId="0" ref="C14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQg
+ID#AAACGNURQgk
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -146,7 +147,7 @@
     <comment authorId="0" ref="H18">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQo
+ID#AAACGNTNROQ
 Unknown Author    (2026-08-28 14:11:25)
 d  For structural bolting: 50 700 N (for M12), 68 800 N (for M14) and 94 500 N (for M16), instead of the table value in the 8.8 column.</t>
       </text>
@@ -154,15 +155,7 @@
     <comment authorId="0" ref="E15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAP8
-Unknown Author    (2026-08-28 14:11:25)
-c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="E14">
-      <text>
-        <t xml:space="preserve">======
-ID#AAACGKLpARI
+ID#AAACGNTNROM
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -170,15 +163,23 @@
     <comment authorId="0" ref="H17">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQI
+ID#AAACGNURQgc
 Unknown Author    (2026-08-28 14:11:25)
 d  For structural bolting: 50 700 N (for M12), 68 800 N (for M14) and 94 500 N (for M16), instead of the table value in the 8.8 column.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E14">
+      <text>
+        <t xml:space="preserve">======
+ID#AAACGNTNROk
+Unknown Author    (2026-08-28 14:11:25)
+c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
     </comment>
     <comment authorId="0" ref="H16">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQQ
+ID#AAACGNTNROc
 Unknown Author    (2026-08-28 14:11:25)
 d  For structural bolting: 50 700 N (for M12), 68 800 N (for M14) and 94 500 N (for M16), instead of the table value in the 8.8 column.</t>
       </text>
@@ -186,7 +187,7 @@
     <comment authorId="0" ref="H15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQ4
+ID#AAACGNURQgg
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -194,7 +195,7 @@
     <comment authorId="0" ref="H14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQM
+ID#AAACGNURQgo
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -202,7 +203,7 @@
     <comment authorId="0" ref="J15">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQ8
+ID#AAACGNURQgs
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -210,7 +211,7 @@
     <comment authorId="0" ref="J14">
       <text>
         <t xml:space="preserve">======
-ID#AAACGKLpAQw
+ID#AAACGNTNROI
 Unknown Author    (2026-08-28 14:11:25)
 c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
       </text>
@@ -218,202 +219,378 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjXmiUTS3zIC9tluRx+7h9WkStuig=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgdouIQf1Z8jxA1rKxTkQhmrNMSQw=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="121">
+  <si>
+    <t>Table 5 — Proof loads</t>
+  </si>
+  <si>
+    <t>Table 4 — Minimum ultimate tensile loads</t>
+  </si>
+  <si>
+    <t>Table 6 — Minimum ultimate tensile loads</t>
+  </si>
+  <si>
+    <t>Table 3 — Mechanical and physical properties of bolts, screws and studs</t>
+  </si>
+  <si>
+    <t>ISO metric fine pitch thread</t>
+  </si>
+  <si>
+    <t>ISO metric coarse pitch thread</t>
+  </si>
+  <si>
+    <t>Source: ISO 898-1:2013(E), © ISO 2013</t>
+  </si>
+  <si>
+    <t>Bolts, screws and studs — coarse thread M1,6 to M39 and fine thread M8×1 to M39×3</t>
+  </si>
+  <si>
+    <t>Property class</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Mechanical or physical property</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>10.9</t>
+  </si>
+  <si>
+    <t>12.9/12.9</t>
+  </si>
+  <si>
+    <t>Proof load, Fp (As,nom × Sp,nom), N</t>
+  </si>
+  <si>
+    <t>M3x0.5</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Minimum ultimate tensile load, Fm,min (As,nom × Rm,min), N</t>
+  </si>
+  <si>
+    <t>M8x1</t>
+  </si>
+  <si>
+    <t>8.8
+(d ≤ 16 mm)</t>
+  </si>
+  <si>
+    <t>8.8
+(d &gt; 16 mm)</t>
+  </si>
+  <si>
+    <t>M3.5x0.6</t>
+  </si>
+  <si>
+    <t>M10x1.25</t>
+  </si>
+  <si>
+    <t>M4x0.7</t>
+  </si>
+  <si>
+    <t>M5x0.8</t>
+  </si>
+  <si>
+    <t>M6x1</t>
+  </si>
+  <si>
+    <t>M7x1</t>
+  </si>
+  <si>
+    <t>M8x1.25</t>
+  </si>
+  <si>
+    <t>M10x1.5</t>
+  </si>
+  <si>
+    <t>Tensile strength, Rm, MPa</t>
+  </si>
+  <si>
+    <t>M12x1.75</t>
+  </si>
+  <si>
+    <t>M14x2</t>
+  </si>
+  <si>
+    <t>M16x2</t>
+  </si>
+  <si>
+    <t>M10x1</t>
+  </si>
+  <si>
+    <t>nom.</t>
+  </si>
+  <si>
+    <t>M18x2.5</t>
+  </si>
+  <si>
+    <t>M12x1.5</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>M20x2.5</t>
+  </si>
+  <si>
+    <t>M12x1.25</t>
+  </si>
+  <si>
+    <t>M22x2.5</t>
+  </si>
+  <si>
+    <t>M24x3</t>
+  </si>
+  <si>
+    <t>M14x1.5</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>M27x3</t>
+  </si>
+  <si>
+    <t>M16x1.5</t>
+  </si>
+  <si>
+    <t>M30x3.5</t>
+  </si>
+  <si>
+    <t>M18x1.5</t>
+  </si>
+  <si>
+    <t>M33x3.5</t>
+  </si>
+  <si>
+    <t>M36x4</t>
+  </si>
+  <si>
+    <t>M20x1.5</t>
+  </si>
+  <si>
+    <t>min.</t>
+  </si>
+  <si>
+    <t>M39x4</t>
+  </si>
+  <si>
+    <t>M22x1.5</t>
+  </si>
+  <si>
+    <t>M24x2</t>
+  </si>
+  <si>
+    <t>M27x2</t>
+  </si>
+  <si>
+    <t>M30x2</t>
+  </si>
+  <si>
+    <t>M33x2</t>
+  </si>
+  <si>
+    <t>Lower yield strength, ReL, MPa</t>
+  </si>
+  <si>
+    <t>M36x3</t>
+  </si>
+  <si>
+    <t>a  Where no thread pitch is indicated in a thread designation, coarse pitch is specified.</t>
+  </si>
+  <si>
+    <t>c, d</t>
+  </si>
+  <si>
+    <t>M39x3</t>
+  </si>
+  <si>
+    <t>b  To calculate As,nom, see 9.1.6.1.</t>
+  </si>
+  <si>
+    <t>c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
+  </si>
+  <si>
+    <t>d  For structural bolting: 70 000 N (for M12), 95 500 N (for M14) and 130 000 N (for M16), instead of the table value in the 8.8 column.</t>
+  </si>
+  <si>
+    <t>a  To calculate As,nom, see 9.1.6.1.</t>
+  </si>
+  <si>
+    <t>Stress at 0.2 % non-proportional elongation, Rp0.2, MPa</t>
+  </si>
+  <si>
+    <t>Stress at 0.0048d non-proportional elongation for full-size fasteners, Rpf, MPa</t>
+  </si>
+  <si>
+    <t>Stress under proof load, Sp, MPa</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Proof strength ratio (Sp,nom / ReL,min or Rp0.2,min or Rpf,min)</t>
+  </si>
+  <si>
+    <t>Percentage elongation after fracture for machined test pieces, A, %</t>
+  </si>
+  <si>
+    <t>Percentage reduction of area after fracture for machined test pieces, Z, %</t>
+  </si>
+  <si>
+    <t>Elongation after fracture for full-size fasteners, Af</t>
+  </si>
+  <si>
+    <t>Head soundness</t>
+  </si>
+  <si>
+    <t>No fracture</t>
+  </si>
+  <si>
+    <t>Vickers hardness, HV (F ≥ 98 N)</t>
+  </si>
+  <si>
+    <t>max.</t>
+  </si>
+  <si>
+    <t>Brinell hardness, HBW (F = 30D²)</t>
+  </si>
+  <si>
+    <t>Rockwell hardness, HRB</t>
+  </si>
+  <si>
+    <t>d  For structural bolting: 50 700 N (for M12), 68 800 N (for M14) and 94 500 N (for M16), instead of the table value in the 8.8 column.</t>
+  </si>
+  <si>
+    <t>Rockwell hardness, HRC</t>
+  </si>
+  <si>
+    <t>Surface hardness, HV 0.3</t>
+  </si>
+  <si>
+    <t>Non-carburization, HV 0.3</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Height of non-decarburized thread zone, E, mm</t>
+  </si>
+  <si>
+    <t>1/2 H1</t>
+  </si>
+  <si>
+    <t>2/3 H1</t>
+  </si>
+  <si>
+    <t>3/4 H1</t>
+  </si>
+  <si>
+    <t>Depth of complete decarburization in the thread, G, mm</t>
+  </si>
+  <si>
+    <t>Reduction of hardness after retempering, HV</t>
+  </si>
+  <si>
+    <t>Breaking torque, MB, Nm</t>
+  </si>
+  <si>
+    <t>in accordance with ISO 898-7</t>
+  </si>
+  <si>
+    <t>Impact strength, Kv, J</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>i, j, k</t>
+  </si>
+  <si>
+    <t>Surface integrity</t>
+  </si>
+  <si>
+    <t>ISO 6157-1</t>
+  </si>
+  <si>
+    <t>ISO 6157-3</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>a  Not applicable to structural bolting.</t>
+  </si>
+  <si>
+    <t>b  For structural bolting, d ≥ M12.</t>
+  </si>
+  <si>
+    <t>c  Nominal values are given only for the purpose of the property-class designation system (see Clause 5).</t>
+  </si>
+  <si>
+    <t>d  Where the lower yield strength, ReL, cannot be determined, the stress at 0,2 % non-proportional elongation, Rp0,2, may be measured instead.</t>
+  </si>
+  <si>
+    <t>e  For property classes 4.8, 5.8 and 6.8, the Rpf,min values are under investigation. The values shown were current at publication and are for calculating the proof strength ratio only — they are not test values.</t>
+  </si>
+  <si>
+    <t>f  Proof loads are specified in Tables 5 and 7.</t>
+  </si>
+  <si>
+    <t>g  Hardness determined at the end of a fastener shall not exceed 250 HV, 238 HBW or 99,5 HRB.</t>
+  </si>
+  <si>
+    <t>h  Surface hardness shall not exceed the measured base metal hardness by more than 30 Vickers points (both determined at HV 0,3).</t>
+  </si>
+  <si>
+    <t>i  Values determined at a test temperature of −20 °C.</t>
+  </si>
+  <si>
+    <t>j  Applies to d ≥ 16 mm.</t>
+  </si>
+  <si>
+    <t>k  The Kv value for property class 12.9/12.9 is under investigation.</t>
+  </si>
+  <si>
+    <t>l  ISO 6157-3 may apply instead of ISO 6157-1 by agreement between the manufacturer and the purchaser.</t>
+  </si>
   <si>
     <t>Table 7 — Proof loads</t>
-  </si>
-  <si>
-    <t>Table 6 — Minimum ultimate tensile loads</t>
-  </si>
-  <si>
-    <t>Table 5 — Proof loads</t>
-  </si>
-  <si>
-    <t>Table 4 — Minimum ultimate tensile loads</t>
-  </si>
-  <si>
-    <t>ISO metric fine pitch thread</t>
-  </si>
-  <si>
-    <t>ISO metric coarse pitch thread</t>
-  </si>
-  <si>
-    <t>Source: ISO 898-1:2013(E), © ISO 2013</t>
-  </si>
-  <si>
-    <t>Property class</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>8.8</t>
-  </si>
-  <si>
-    <t>9.8</t>
-  </si>
-  <si>
-    <t>10.9</t>
-  </si>
-  <si>
-    <t>12.9/12.9</t>
-  </si>
-  <si>
-    <t>Minimum ultimate tensile load, Fm,min (As,nom × Rm,min), N</t>
-  </si>
-  <si>
-    <t>Proof load, Fp (As,nom × Sp,nom), N</t>
-  </si>
-  <si>
-    <t>M3x0.5</t>
-  </si>
-  <si>
-    <t>M8x1</t>
-  </si>
-  <si>
-    <t>M3.5x0.6</t>
-  </si>
-  <si>
-    <t>M10x1.25</t>
-  </si>
-  <si>
-    <t>M4x0.7</t>
-  </si>
-  <si>
-    <t>M10x1</t>
-  </si>
-  <si>
-    <t>M5x0.8</t>
-  </si>
-  <si>
-    <t>M12x1.5</t>
-  </si>
-  <si>
-    <t>M6x1</t>
-  </si>
-  <si>
-    <t>M7x1</t>
-  </si>
-  <si>
-    <t>M12x1.25</t>
-  </si>
-  <si>
-    <t>M8x1.25</t>
-  </si>
-  <si>
-    <t>M14x1.5</t>
-  </si>
-  <si>
-    <t>M10x1.5</t>
-  </si>
-  <si>
-    <t>M16x1.5</t>
-  </si>
-  <si>
-    <t>M18x1.5</t>
-  </si>
-  <si>
-    <t>M12x1.75</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>M14x2</t>
-  </si>
-  <si>
-    <t>M20x1.5</t>
-  </si>
-  <si>
-    <t>M16x2</t>
-  </si>
-  <si>
-    <t>M22x1.5</t>
-  </si>
-  <si>
-    <t>M18x2.5</t>
-  </si>
-  <si>
-    <t>M24x2</t>
-  </si>
-  <si>
-    <t>M20x2.5</t>
-  </si>
-  <si>
-    <t>M27x2</t>
-  </si>
-  <si>
-    <t>M22x2.5</t>
-  </si>
-  <si>
-    <t>M30x2</t>
-  </si>
-  <si>
-    <t>M24x3</t>
-  </si>
-  <si>
-    <t>M33x2</t>
-  </si>
-  <si>
-    <t>M27x3</t>
-  </si>
-  <si>
-    <t>M36x3</t>
-  </si>
-  <si>
-    <t>M39x3</t>
-  </si>
-  <si>
-    <t>M30x3.5</t>
-  </si>
-  <si>
-    <t>M33x3.5</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>a  To calculate As,nom, see 9.1.6.1.</t>
-  </si>
-  <si>
-    <t>M36x4</t>
-  </si>
-  <si>
-    <t>M39x4</t>
-  </si>
-  <si>
-    <t>a  Where no thread pitch is indicated in a thread designation, coarse pitch is specified.</t>
-  </si>
-  <si>
-    <t>b  To calculate As,nom, see 9.1.6.1.</t>
-  </si>
-  <si>
-    <t>c  For fasteners with thread tolerance 6az in accordance with ISO 965-4 subject to hot dip galvanizing, reduced values in accordance with ISO 10684:2004, Annex A, apply. (Marked cells: M8, M10 — columns 4.6, 5.6, 8.8, 10.9)</t>
-  </si>
-  <si>
-    <t>d  For structural bolting: 70 000 N (for M12), 95 500 N (for M14) and 130 000 N (for M16), instead of the table value in the 8.8 column.</t>
-  </si>
-  <si>
-    <t>d  For structural bolting: 50 700 N (for M12), 68 800 N (for M14) and 94 500 N (for M16), instead of the table value in the 8.8 column.</t>
   </si>
 </sst>
 </file>
@@ -423,7 +600,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -454,9 +631,19 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF404040"/>
       <name val="Arial"/>
     </font>
     <font/>
@@ -474,6 +661,13 @@
     </font>
     <font>
       <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -498,7 +692,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border/>
     <border>
       <right style="thin">
@@ -514,6 +708,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
@@ -555,11 +779,47 @@
         <color rgb="FFB7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="44">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -575,47 +835,110 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="0" fontId="11" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="11" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,6 +961,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -842,10 +1169,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.0"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="6.0"/>
+    <col customWidth="1" min="2" max="2" width="46.0"/>
+    <col customWidth="1" min="3" max="3" width="8.0"/>
+    <col customWidth="1" min="4" max="13" width="12.43"/>
+    <col customWidth="1" min="14" max="14" width="10.0"/>
+    <col customWidth="1" min="15" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,809 +1183,1341 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="8" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="E6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="F6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="G6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="H6" s="20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="s">
+      <c r="I6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="12">
-        <v>5.03</v>
-      </c>
-      <c r="C8" s="14">
-        <v>2010.0</v>
-      </c>
-      <c r="D8" s="14">
-        <v>2110.0</v>
-      </c>
-      <c r="E8" s="14">
-        <v>2510.0</v>
-      </c>
-      <c r="F8" s="14">
-        <v>2620.0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>3020.0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>4020.0</v>
-      </c>
-      <c r="I8" s="14">
-        <v>4530.0</v>
-      </c>
-      <c r="J8" s="14">
-        <v>5230.0</v>
-      </c>
-      <c r="K8" s="14">
-        <v>6140.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="16">
-        <v>6.78</v>
-      </c>
-      <c r="C9" s="17">
-        <v>2710.0</v>
-      </c>
-      <c r="D9" s="17">
-        <v>2850.0</v>
-      </c>
-      <c r="E9" s="17">
-        <v>3390.0</v>
-      </c>
-      <c r="F9" s="17">
-        <v>3530.0</v>
-      </c>
-      <c r="G9" s="17">
-        <v>4070.0</v>
-      </c>
-      <c r="H9" s="17">
-        <v>5420.0</v>
-      </c>
-      <c r="I9" s="17">
-        <v>6100.0</v>
-      </c>
-      <c r="J9" s="17">
-        <v>7050.0</v>
-      </c>
-      <c r="K9" s="17">
-        <v>8270.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="s">
+      <c r="M6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" ht="25.5" customHeight="1">
+      <c r="A7" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="27">
+        <v>400.0</v>
+      </c>
+      <c r="E7" s="27">
+        <v>400.0</v>
+      </c>
+      <c r="F7" s="27">
+        <v>500.0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>500.0</v>
+      </c>
+      <c r="H7" s="27">
+        <v>600.0</v>
+      </c>
+      <c r="I7" s="27">
+        <v>800.0</v>
+      </c>
+      <c r="J7" s="27">
+        <v>800.0</v>
+      </c>
+      <c r="K7" s="27">
+        <v>900.0</v>
+      </c>
+      <c r="L7" s="27">
+        <v>1000.0</v>
+      </c>
+      <c r="M7" s="27">
+        <v>1200.0</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" ht="25.5" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="29">
+        <v>400.0</v>
+      </c>
+      <c r="E8" s="29">
+        <v>420.0</v>
+      </c>
+      <c r="F8" s="29">
+        <v>500.0</v>
+      </c>
+      <c r="G8" s="29">
+        <v>520.0</v>
+      </c>
+      <c r="H8" s="29">
+        <v>600.0</v>
+      </c>
+      <c r="I8" s="29">
+        <v>800.0</v>
+      </c>
+      <c r="J8" s="29">
+        <v>830.0</v>
+      </c>
+      <c r="K8" s="29">
+        <v>900.0</v>
+      </c>
+      <c r="L8" s="29">
+        <v>1040.0</v>
+      </c>
+      <c r="M8" s="29">
+        <v>1220.0</v>
+      </c>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" ht="25.5" customHeight="1">
+      <c r="A9" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="27">
+        <v>240.0</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="27">
+        <v>300.0</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" ht="25.5" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="29">
+        <v>240.0</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="29">
+        <v>300.0</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" ht="25.5" customHeight="1">
+      <c r="A11" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="27">
+        <v>640.0</v>
+      </c>
+      <c r="J11" s="27">
+        <v>640.0</v>
+      </c>
+      <c r="K11" s="27">
+        <v>720.0</v>
+      </c>
+      <c r="L11" s="27">
+        <v>900.0</v>
+      </c>
+      <c r="M11" s="27">
+        <v>1080.0</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" ht="25.5" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="29">
+        <v>640.0</v>
+      </c>
+      <c r="J12" s="29">
+        <v>660.0</v>
+      </c>
+      <c r="K12" s="29">
+        <v>720.0</v>
+      </c>
+      <c r="L12" s="29">
+        <v>940.0</v>
+      </c>
+      <c r="M12" s="29">
+        <v>1100.0</v>
+      </c>
+      <c r="N12" s="19"/>
+    </row>
+    <row r="13" ht="25.5" customHeight="1">
+      <c r="A13" s="25">
+        <v>4.0</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="27">
+        <v>320.0</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="27">
+        <v>400.0</v>
+      </c>
+      <c r="H13" s="27">
+        <v>480.0</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="29">
+        <v>340.0</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="29">
+        <v>420.0</v>
+      </c>
+      <c r="H14" s="29">
+        <v>480.0</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" ht="25.5" customHeight="1">
+      <c r="A15" s="33">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="27">
+        <v>225.0</v>
+      </c>
+      <c r="E15" s="27">
+        <v>310.0</v>
+      </c>
+      <c r="F15" s="27">
+        <v>280.0</v>
+      </c>
+      <c r="G15" s="27">
+        <v>380.0</v>
+      </c>
+      <c r="H15" s="27">
+        <v>440.0</v>
+      </c>
+      <c r="I15" s="27">
+        <v>580.0</v>
+      </c>
+      <c r="J15" s="27">
+        <v>600.0</v>
+      </c>
+      <c r="K15" s="27">
+        <v>650.0</v>
+      </c>
+      <c r="L15" s="27">
+        <v>830.0</v>
+      </c>
+      <c r="M15" s="27">
+        <v>970.0</v>
+      </c>
+      <c r="N15" s="35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" ht="25.5" customHeight="1">
+      <c r="A16" s="36">
+        <v>5.0</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="29">
+        <v>0.94</v>
+      </c>
+      <c r="E16" s="29">
+        <v>0.91</v>
+      </c>
+      <c r="F16" s="29">
+        <v>0.93</v>
+      </c>
+      <c r="G16" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="H16" s="29">
+        <v>0.92</v>
+      </c>
+      <c r="I16" s="29">
+        <v>0.91</v>
+      </c>
+      <c r="J16" s="29">
+        <v>0.91</v>
+      </c>
+      <c r="K16" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="L16" s="29">
+        <v>0.88</v>
+      </c>
+      <c r="M16" s="29">
+        <v>0.88</v>
+      </c>
+      <c r="N16" s="38"/>
+    </row>
+    <row r="17" ht="25.5" customHeight="1">
+      <c r="A17" s="33">
+        <v>6.0</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="27">
+        <v>22.0</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="27">
+        <v>20.0</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="27">
+        <v>12.0</v>
+      </c>
+      <c r="J17" s="27">
+        <v>12.0</v>
+      </c>
+      <c r="K17" s="27">
+        <v>10.0</v>
+      </c>
+      <c r="L17" s="27">
+        <v>9.0</v>
+      </c>
+      <c r="M17" s="27">
+        <v>8.0</v>
+      </c>
+      <c r="N17" s="35"/>
+    </row>
+    <row r="18" ht="25.5" customHeight="1">
+      <c r="A18" s="36">
+        <v>7.0</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="29">
+        <v>52.0</v>
+      </c>
+      <c r="J18" s="29">
+        <v>52.0</v>
+      </c>
+      <c r="K18" s="29">
+        <v>48.0</v>
+      </c>
+      <c r="L18" s="29">
+        <v>48.0</v>
+      </c>
+      <c r="M18" s="29">
+        <v>44.0</v>
+      </c>
+      <c r="N18" s="38"/>
+    </row>
+    <row r="19" ht="25.5" customHeight="1">
+      <c r="A19" s="33">
+        <v>8.0</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="27">
+        <v>0.24</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="27">
+        <v>0.22</v>
+      </c>
+      <c r="H19" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" s="35"/>
+    </row>
+    <row r="20" ht="25.5" customHeight="1">
+      <c r="A20" s="36">
+        <v>9.0</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="38"/>
+    </row>
+    <row r="21" ht="25.5" customHeight="1">
+      <c r="A21" s="25">
+        <v>10.0</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="27">
+        <v>120.0</v>
+      </c>
+      <c r="E21" s="27">
+        <v>130.0</v>
+      </c>
+      <c r="F21" s="27">
+        <v>155.0</v>
+      </c>
+      <c r="G21" s="27">
+        <v>160.0</v>
+      </c>
+      <c r="H21" s="27">
+        <v>190.0</v>
+      </c>
+      <c r="I21" s="27">
+        <v>250.0</v>
+      </c>
+      <c r="J21" s="27">
+        <v>255.0</v>
+      </c>
+      <c r="K21" s="27">
+        <v>290.0</v>
+      </c>
+      <c r="L21" s="27">
+        <v>320.0</v>
+      </c>
+      <c r="M21" s="27">
+        <v>385.0</v>
+      </c>
+      <c r="N21" s="28"/>
+    </row>
+    <row r="22" ht="25.5" customHeight="1">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="29">
+        <v>220.0</v>
+      </c>
+      <c r="E22" s="29">
+        <v>220.0</v>
+      </c>
+      <c r="F22" s="29">
+        <v>220.0</v>
+      </c>
+      <c r="G22" s="29">
+        <v>220.0</v>
+      </c>
+      <c r="H22" s="29">
+        <v>250.0</v>
+      </c>
+      <c r="I22" s="29">
+        <v>320.0</v>
+      </c>
+      <c r="J22" s="29">
+        <v>335.0</v>
+      </c>
+      <c r="K22" s="29">
+        <v>360.0</v>
+      </c>
+      <c r="L22" s="29">
+        <v>380.0</v>
+      </c>
+      <c r="M22" s="29">
+        <v>435.0</v>
+      </c>
+      <c r="N22" s="19"/>
+    </row>
+    <row r="23" ht="25.5" customHeight="1">
+      <c r="A23" s="25">
+        <v>11.0</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="27">
+        <v>114.0</v>
+      </c>
+      <c r="E23" s="27">
+        <v>124.0</v>
+      </c>
+      <c r="F23" s="27">
+        <v>147.0</v>
+      </c>
+      <c r="G23" s="27">
+        <v>152.0</v>
+      </c>
+      <c r="H23" s="27">
+        <v>181.0</v>
+      </c>
+      <c r="I23" s="27">
+        <v>245.0</v>
+      </c>
+      <c r="J23" s="27">
+        <v>250.0</v>
+      </c>
+      <c r="K23" s="27">
+        <v>286.0</v>
+      </c>
+      <c r="L23" s="27">
+        <v>316.0</v>
+      </c>
+      <c r="M23" s="27">
+        <v>380.0</v>
+      </c>
+      <c r="N23" s="28"/>
+    </row>
+    <row r="24" ht="25.5" customHeight="1">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="29">
+        <v>209.0</v>
+      </c>
+      <c r="E24" s="29">
+        <v>209.0</v>
+      </c>
+      <c r="F24" s="29">
+        <v>209.0</v>
+      </c>
+      <c r="G24" s="29">
+        <v>209.0</v>
+      </c>
+      <c r="H24" s="29">
+        <v>238.0</v>
+      </c>
+      <c r="I24" s="29">
+        <v>316.0</v>
+      </c>
+      <c r="J24" s="29">
+        <v>331.0</v>
+      </c>
+      <c r="K24" s="29">
+        <v>355.0</v>
+      </c>
+      <c r="L24" s="29">
+        <v>375.0</v>
+      </c>
+      <c r="M24" s="29">
+        <v>429.0</v>
+      </c>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25" s="25">
+        <v>12.0</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="27">
+        <v>67.0</v>
+      </c>
+      <c r="E25" s="27">
+        <v>71.0</v>
+      </c>
+      <c r="F25" s="27">
+        <v>79.0</v>
+      </c>
+      <c r="G25" s="27">
+        <v>82.0</v>
+      </c>
+      <c r="H25" s="27">
+        <v>89.0</v>
+      </c>
+      <c r="I25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="M25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N25" s="28"/>
+    </row>
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="29">
+        <v>95.0</v>
+      </c>
+      <c r="E26" s="29">
+        <v>95.0</v>
+      </c>
+      <c r="F26" s="29">
+        <v>95.0</v>
+      </c>
+      <c r="G26" s="29">
+        <v>95.0</v>
+      </c>
+      <c r="H26" s="29">
+        <v>99.5</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" s="19"/>
+    </row>
+    <row r="27" ht="25.5" customHeight="1">
+      <c r="A27" s="25">
+        <v>12.0</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="27">
+        <v>22.0</v>
+      </c>
+      <c r="J27" s="27">
+        <v>23.0</v>
+      </c>
+      <c r="K27" s="27">
+        <v>28.0</v>
+      </c>
+      <c r="L27" s="27">
+        <v>32.0</v>
+      </c>
+      <c r="M27" s="27">
+        <v>39.0</v>
+      </c>
+      <c r="N27" s="28"/>
+    </row>
+    <row r="28" ht="25.5" customHeight="1">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="29">
+        <v>32.0</v>
+      </c>
+      <c r="J28" s="29">
+        <v>34.0</v>
+      </c>
+      <c r="K28" s="29">
+        <v>37.0</v>
+      </c>
+      <c r="L28" s="29">
+        <v>39.0</v>
+      </c>
+      <c r="M28" s="29">
+        <v>44.0</v>
+      </c>
+      <c r="N28" s="19"/>
+    </row>
+    <row r="29" ht="25.5" customHeight="1">
+      <c r="A29" s="33">
+        <v>13.0</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" s="27">
+        <v>390.0</v>
+      </c>
+      <c r="M29" s="27">
+        <v>435.0</v>
+      </c>
+      <c r="N29" s="35"/>
+    </row>
+    <row r="30" ht="25.5" customHeight="1">
+      <c r="A30" s="36">
+        <v>14.0</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="M30" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="N30" s="38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" ht="25.5" customHeight="1">
+      <c r="A31" s="33">
+        <v>15.0</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="J31" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="K31" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="M31" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="N31" s="35"/>
+    </row>
+    <row r="32" ht="25.5" customHeight="1">
+      <c r="A32" s="36">
+        <v>15.0</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="29">
+        <v>0.015</v>
+      </c>
+      <c r="J32" s="29">
+        <v>0.015</v>
+      </c>
+      <c r="K32" s="29">
+        <v>0.015</v>
+      </c>
+      <c r="L32" s="29">
+        <v>0.015</v>
+      </c>
+      <c r="M32" s="29">
+        <v>0.015</v>
+      </c>
+      <c r="N32" s="38"/>
+    </row>
+    <row r="33" ht="25.5" customHeight="1">
+      <c r="A33" s="33">
+        <v>16.0</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="27">
+        <v>20.0</v>
+      </c>
+      <c r="J33" s="27">
+        <v>20.0</v>
+      </c>
+      <c r="K33" s="27">
+        <v>20.0</v>
+      </c>
+      <c r="L33" s="27">
+        <v>20.0</v>
+      </c>
+      <c r="M33" s="27">
+        <v>20.0</v>
+      </c>
+      <c r="N33" s="35"/>
+    </row>
+    <row r="34" ht="25.5" customHeight="1">
+      <c r="A34" s="36">
+        <v>17.0</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="38"/>
+    </row>
+    <row r="35" ht="25.5" customHeight="1">
+      <c r="A35" s="33">
+        <v>18.0</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="27">
+        <v>27.0</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I35" s="27">
+        <v>27.0</v>
+      </c>
+      <c r="J35" s="27">
+        <v>27.0</v>
+      </c>
+      <c r="K35" s="27">
+        <v>27.0</v>
+      </c>
+      <c r="L35" s="27">
+        <v>27.0</v>
+      </c>
+      <c r="M35" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="N35" s="35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" ht="25.5" customHeight="1">
+      <c r="A36" s="36">
+        <v>19.0</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="29"/>
+      <c r="D36" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="N36" s="38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.0" customHeight="1">
+      <c r="A38" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="12">
-        <v>8.78</v>
-      </c>
-      <c r="C10" s="14">
-        <v>3510.0</v>
-      </c>
-      <c r="D10" s="14">
-        <v>3690.0</v>
-      </c>
-      <c r="E10" s="14">
-        <v>4390.0</v>
-      </c>
-      <c r="F10" s="14">
-        <v>4570.0</v>
-      </c>
-      <c r="G10" s="14">
-        <v>5270.0</v>
-      </c>
-      <c r="H10" s="14">
-        <v>7020.0</v>
-      </c>
-      <c r="I10" s="14">
-        <v>7900.0</v>
-      </c>
-      <c r="J10" s="14">
-        <v>9130.0</v>
-      </c>
-      <c r="K10" s="14">
-        <v>10700.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="16">
-        <v>14.2</v>
-      </c>
-      <c r="C11" s="17">
-        <v>5680.0</v>
-      </c>
-      <c r="D11" s="17">
-        <v>5960.0</v>
-      </c>
-      <c r="E11" s="17">
-        <v>7100.0</v>
-      </c>
-      <c r="F11" s="17">
-        <v>7380.0</v>
-      </c>
-      <c r="G11" s="17">
-        <v>8520.0</v>
-      </c>
-      <c r="H11" s="17">
-        <v>11350.0</v>
-      </c>
-      <c r="I11" s="17">
-        <v>12800.0</v>
-      </c>
-      <c r="J11" s="17">
-        <v>14800.0</v>
-      </c>
-      <c r="K11" s="17">
-        <v>17300.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="12">
-        <v>20.1</v>
-      </c>
-      <c r="C12" s="14">
-        <v>8040.0</v>
-      </c>
-      <c r="D12" s="14">
-        <v>8440.0</v>
-      </c>
-      <c r="E12" s="14">
-        <v>10000.0</v>
-      </c>
-      <c r="F12" s="14">
-        <v>10400.0</v>
-      </c>
-      <c r="G12" s="14">
-        <v>12100.0</v>
-      </c>
-      <c r="H12" s="14">
-        <v>16100.0</v>
-      </c>
-      <c r="I12" s="14">
-        <v>18100.0</v>
-      </c>
-      <c r="J12" s="14">
-        <v>20900.0</v>
-      </c>
-      <c r="K12" s="14">
-        <v>24500.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="16">
-        <v>28.9</v>
-      </c>
-      <c r="C13" s="17">
-        <v>11600.0</v>
-      </c>
-      <c r="D13" s="17">
-        <v>12100.0</v>
-      </c>
-      <c r="E13" s="17">
-        <v>14400.0</v>
-      </c>
-      <c r="F13" s="17">
-        <v>15000.0</v>
-      </c>
-      <c r="G13" s="17">
-        <v>17300.0</v>
-      </c>
-      <c r="H13" s="17">
-        <v>23100.0</v>
-      </c>
-      <c r="I13" s="17">
-        <v>26000.0</v>
-      </c>
-      <c r="J13" s="17">
-        <v>30100.0</v>
-      </c>
-      <c r="K13" s="17">
-        <v>35300.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="12">
-        <v>36.6</v>
-      </c>
-      <c r="C14" s="14">
-        <v>14600.0</v>
-      </c>
-      <c r="D14" s="14">
-        <v>15400.0</v>
-      </c>
-      <c r="E14" s="14">
-        <v>18300.0</v>
-      </c>
-      <c r="F14" s="14">
-        <v>19000.0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>22000.0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>29200.0</v>
-      </c>
-      <c r="I14" s="14">
-        <v>32900.0</v>
-      </c>
-      <c r="J14" s="14">
-        <v>38100.0</v>
-      </c>
-      <c r="K14" s="14">
-        <v>44600.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="16">
-        <v>58.0</v>
-      </c>
-      <c r="C15" s="17">
-        <v>23200.0</v>
-      </c>
-      <c r="D15" s="17">
-        <v>24400.0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>29000.0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>30200.0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>34800.0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>46400.0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>52200.0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>60300.0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>70800.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="12">
-        <v>84.3</v>
-      </c>
-      <c r="C16" s="14">
-        <v>33700.0</v>
-      </c>
-      <c r="D16" s="14">
-        <v>35400.0</v>
-      </c>
-      <c r="E16" s="14">
-        <v>42200.0</v>
-      </c>
-      <c r="F16" s="14">
-        <v>43800.0</v>
-      </c>
-      <c r="G16" s="14">
-        <v>50600.0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>67400.0</v>
-      </c>
-      <c r="I16" s="14">
-        <v>75900.0</v>
-      </c>
-      <c r="J16" s="14">
-        <v>87700.0</v>
-      </c>
-      <c r="K16" s="14">
-        <v>103000.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="16">
-        <v>115.0</v>
-      </c>
-      <c r="C17" s="17">
-        <v>46000.0</v>
-      </c>
-      <c r="D17" s="17">
-        <v>48300.0</v>
-      </c>
-      <c r="E17" s="17">
-        <v>57500.0</v>
-      </c>
-      <c r="F17" s="17">
-        <v>59800.0</v>
-      </c>
-      <c r="G17" s="17">
-        <v>69000.0</v>
-      </c>
-      <c r="H17" s="17">
-        <v>92000.0</v>
-      </c>
-      <c r="I17" s="17">
-        <v>104000.0</v>
-      </c>
-      <c r="J17" s="17">
-        <v>120000.0</v>
-      </c>
-      <c r="K17" s="17">
-        <v>140000.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="12">
-        <v>157.0</v>
-      </c>
-      <c r="C18" s="14">
-        <v>62800.0</v>
-      </c>
-      <c r="D18" s="14">
-        <v>65900.0</v>
-      </c>
-      <c r="E18" s="14">
-        <v>78500.0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>81600.0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>94000.0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>125000.0</v>
-      </c>
-      <c r="I18" s="14">
-        <v>141000.0</v>
-      </c>
-      <c r="J18" s="14">
-        <v>163000.0</v>
-      </c>
-      <c r="K18" s="14">
-        <v>192000.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="16">
-        <v>192.0</v>
-      </c>
-      <c r="C19" s="17">
-        <v>76800.0</v>
-      </c>
-      <c r="D19" s="17">
-        <v>80600.0</v>
-      </c>
-      <c r="E19" s="17">
-        <v>96000.0</v>
-      </c>
-      <c r="F19" s="17">
-        <v>99800.0</v>
-      </c>
-      <c r="G19" s="17">
-        <v>115000.0</v>
-      </c>
-      <c r="H19" s="17">
-        <v>159000.0</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="17">
-        <v>200000.0</v>
-      </c>
-      <c r="K19" s="17">
-        <v>234000.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="12">
-        <v>245.0</v>
-      </c>
-      <c r="C20" s="14">
-        <v>98000.0</v>
-      </c>
-      <c r="D20" s="14">
-        <v>103000.0</v>
-      </c>
-      <c r="E20" s="14">
-        <v>122000.0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>127000.0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>147000.0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>203000.0</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="14">
-        <v>255000.0</v>
-      </c>
-      <c r="K20" s="14">
-        <v>299000.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="16">
-        <v>303.0</v>
-      </c>
-      <c r="C21" s="17">
-        <v>121000.0</v>
-      </c>
-      <c r="D21" s="17">
-        <v>127000.0</v>
-      </c>
-      <c r="E21" s="17">
-        <v>152000.0</v>
-      </c>
-      <c r="F21" s="17">
-        <v>158000.0</v>
-      </c>
-      <c r="G21" s="17">
-        <v>182000.0</v>
-      </c>
-      <c r="H21" s="17">
-        <v>252000.0</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="17">
-        <v>315000.0</v>
-      </c>
-      <c r="K21" s="17">
-        <v>370000.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="12">
-        <v>353.0</v>
-      </c>
-      <c r="C22" s="14">
-        <v>141000.0</v>
-      </c>
-      <c r="D22" s="14">
-        <v>148000.0</v>
-      </c>
-      <c r="E22" s="14">
-        <v>176000.0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>184000.0</v>
-      </c>
-      <c r="G22" s="14">
-        <v>212000.0</v>
-      </c>
-      <c r="H22" s="14">
-        <v>293000.0</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="14">
-        <v>367000.0</v>
-      </c>
-      <c r="K22" s="14">
-        <v>431000.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="16">
-        <v>459.0</v>
-      </c>
-      <c r="C23" s="17">
-        <v>184000.0</v>
-      </c>
-      <c r="D23" s="17">
-        <v>193000.0</v>
-      </c>
-      <c r="E23" s="17">
-        <v>230000.0</v>
-      </c>
-      <c r="F23" s="17">
-        <v>239000.0</v>
-      </c>
-      <c r="G23" s="17">
-        <v>275000.0</v>
-      </c>
-      <c r="H23" s="17">
-        <v>381000.0</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="17">
-        <v>477000.0</v>
-      </c>
-      <c r="K23" s="17">
-        <v>560000.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="12">
-        <v>561.0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>224000.0</v>
-      </c>
-      <c r="D24" s="14">
-        <v>236000.0</v>
-      </c>
-      <c r="E24" s="14">
-        <v>280000.0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>292000.0</v>
-      </c>
-      <c r="G24" s="14">
-        <v>337000.0</v>
-      </c>
-      <c r="H24" s="14">
-        <v>466000.0</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="14">
-        <v>583000.0</v>
-      </c>
-      <c r="K24" s="14">
-        <v>684000.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="16">
-        <v>694.0</v>
-      </c>
-      <c r="C25" s="17">
-        <v>278000.0</v>
-      </c>
-      <c r="D25" s="17">
-        <v>292000.0</v>
-      </c>
-      <c r="E25" s="17">
-        <v>347000.0</v>
-      </c>
-      <c r="F25" s="17">
-        <v>361000.0</v>
-      </c>
-      <c r="G25" s="17">
-        <v>416000.0</v>
-      </c>
-      <c r="H25" s="17">
-        <v>576000.0</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="17">
-        <v>722000.0</v>
-      </c>
-      <c r="K25" s="17">
-        <v>847000.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="12">
-        <v>817.0</v>
-      </c>
-      <c r="C26" s="14">
-        <v>327000.0</v>
-      </c>
-      <c r="D26" s="14">
-        <v>343000.0</v>
-      </c>
-      <c r="E26" s="14">
-        <v>408000.0</v>
-      </c>
-      <c r="F26" s="14">
-        <v>425000.0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>490000.0</v>
-      </c>
-      <c r="H26" s="14">
-        <v>678000.0</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" s="14">
-        <v>850000.0</v>
-      </c>
-      <c r="K26" s="14">
-        <v>997000.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="16">
-        <v>976.0</v>
-      </c>
-      <c r="C27" s="17">
-        <v>390000.0</v>
-      </c>
-      <c r="D27" s="17">
-        <v>410000.0</v>
-      </c>
-      <c r="E27" s="17">
-        <v>488000.0</v>
-      </c>
-      <c r="F27" s="17">
-        <v>508000.0</v>
-      </c>
-      <c r="G27" s="17">
-        <v>586000.0</v>
-      </c>
-      <c r="H27" s="17">
-        <v>810000.0</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="17">
-        <v>1020000.0</v>
-      </c>
-      <c r="K27" s="17">
-        <v>1200000.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" ht="21.75" customHeight="1">
-      <c r="A33" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="39" ht="15.0" customHeight="1">
+      <c r="A39" s="43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" ht="15.0" customHeight="1">
+      <c r="A40" s="43" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" ht="15.0" customHeight="1">
+      <c r="A42" s="43" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" ht="15.0" customHeight="1">
+      <c r="A43" s="43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" ht="15.0" customHeight="1">
+      <c r="A45" s="43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="A46" s="43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="A47" s="43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" ht="15.0" customHeight="1">
+      <c r="A48" s="43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" ht="15.0" customHeight="1">
+      <c r="A49" s="43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" ht="15.0" customHeight="1">
+      <c r="A50" s="43" t="s">
+        <v>119</v>
+      </c>
+    </row>
     <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
@@ -2608,24 +3469,60 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A31:K31"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
+  <mergeCells count="48">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:M5"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D20:M20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A49:N49"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A48:N48"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2639,12 +3536,11 @@
     <col customWidth="1" min="1" max="1" width="12.0"/>
     <col customWidth="1" min="2" max="2" width="14.0"/>
     <col customWidth="1" min="3" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -2660,779 +3556,779 @@
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="D6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="E6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="F6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="G6" s="14" t="s">
         <v>16</v>
       </c>
+      <c r="H6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>18</v>
+      <c r="A7" s="15" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="17">
         <v>5.03</v>
       </c>
-      <c r="C8" s="14">
-        <v>1130.0</v>
-      </c>
-      <c r="D8" s="14">
-        <v>1560.0</v>
-      </c>
-      <c r="E8" s="14">
-        <v>1410.0</v>
-      </c>
-      <c r="F8" s="14">
-        <v>1910.0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>2210.0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>2920.0</v>
-      </c>
-      <c r="I8" s="14">
-        <v>3270.0</v>
-      </c>
-      <c r="J8" s="14">
-        <v>4180.0</v>
-      </c>
-      <c r="K8" s="14">
-        <v>4880.0</v>
+      <c r="C8" s="21">
+        <v>2010.0</v>
+      </c>
+      <c r="D8" s="21">
+        <v>2110.0</v>
+      </c>
+      <c r="E8" s="21">
+        <v>2510.0</v>
+      </c>
+      <c r="F8" s="21">
+        <v>2620.0</v>
+      </c>
+      <c r="G8" s="21">
+        <v>3020.0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>4020.0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>4530.0</v>
+      </c>
+      <c r="J8" s="21">
+        <v>5230.0</v>
+      </c>
+      <c r="K8" s="21">
+        <v>6140.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="23">
         <v>6.78</v>
       </c>
-      <c r="C9" s="17">
-        <v>1530.0</v>
-      </c>
-      <c r="D9" s="17">
-        <v>2100.0</v>
-      </c>
-      <c r="E9" s="17">
-        <v>1900.0</v>
-      </c>
-      <c r="F9" s="17">
-        <v>2580.0</v>
-      </c>
-      <c r="G9" s="17">
-        <v>2980.0</v>
-      </c>
-      <c r="H9" s="17">
-        <v>3940.0</v>
-      </c>
-      <c r="I9" s="17">
-        <v>4410.0</v>
-      </c>
-      <c r="J9" s="17">
-        <v>5630.0</v>
-      </c>
-      <c r="K9" s="17">
-        <v>6580.0</v>
+      <c r="C9" s="24">
+        <v>2710.0</v>
+      </c>
+      <c r="D9" s="24">
+        <v>2850.0</v>
+      </c>
+      <c r="E9" s="24">
+        <v>3390.0</v>
+      </c>
+      <c r="F9" s="24">
+        <v>3530.0</v>
+      </c>
+      <c r="G9" s="24">
+        <v>4070.0</v>
+      </c>
+      <c r="H9" s="24">
+        <v>5420.0</v>
+      </c>
+      <c r="I9" s="24">
+        <v>6100.0</v>
+      </c>
+      <c r="J9" s="24">
+        <v>7050.0</v>
+      </c>
+      <c r="K9" s="24">
+        <v>8270.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="17">
         <v>8.78</v>
       </c>
-      <c r="C10" s="14">
-        <v>1980.0</v>
-      </c>
-      <c r="D10" s="14">
-        <v>2720.0</v>
-      </c>
-      <c r="E10" s="14">
-        <v>2460.0</v>
-      </c>
-      <c r="F10" s="14">
-        <v>3340.0</v>
-      </c>
-      <c r="G10" s="14">
-        <v>3860.0</v>
-      </c>
-      <c r="H10" s="14">
-        <v>5100.0</v>
-      </c>
-      <c r="I10" s="14">
-        <v>5710.0</v>
-      </c>
-      <c r="J10" s="14">
-        <v>7290.0</v>
-      </c>
-      <c r="K10" s="14">
+      <c r="C10" s="21">
+        <v>3510.0</v>
+      </c>
+      <c r="D10" s="21">
+        <v>3690.0</v>
+      </c>
+      <c r="E10" s="21">
+        <v>4390.0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>4570.0</v>
+      </c>
+      <c r="G10" s="21">
+        <v>5270.0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>7020.0</v>
+      </c>
+      <c r="I10" s="21">
+        <v>7900.0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>9130.0</v>
+      </c>
+      <c r="K10" s="21">
+        <v>10700.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="23">
+        <v>14.2</v>
+      </c>
+      <c r="C11" s="24">
+        <v>5680.0</v>
+      </c>
+      <c r="D11" s="24">
+        <v>5960.0</v>
+      </c>
+      <c r="E11" s="24">
+        <v>7100.0</v>
+      </c>
+      <c r="F11" s="24">
+        <v>7380.0</v>
+      </c>
+      <c r="G11" s="24">
         <v>8520.0</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="16">
-        <v>14.2</v>
-      </c>
-      <c r="C11" s="17">
-        <v>3200.0</v>
-      </c>
-      <c r="D11" s="17">
-        <v>4400.0</v>
-      </c>
-      <c r="E11" s="17">
-        <v>3980.0</v>
-      </c>
-      <c r="F11" s="17">
-        <v>5400.0</v>
-      </c>
-      <c r="G11" s="17">
-        <v>6250.0</v>
-      </c>
-      <c r="H11" s="17">
-        <v>8230.0</v>
-      </c>
-      <c r="I11" s="17">
-        <v>9230.0</v>
-      </c>
-      <c r="J11" s="17">
-        <v>11800.0</v>
-      </c>
-      <c r="K11" s="17">
-        <v>13800.0</v>
+      <c r="H11" s="24">
+        <v>11350.0</v>
+      </c>
+      <c r="I11" s="24">
+        <v>12800.0</v>
+      </c>
+      <c r="J11" s="24">
+        <v>14800.0</v>
+      </c>
+      <c r="K11" s="24">
+        <v>17300.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="17">
         <v>20.1</v>
       </c>
-      <c r="C12" s="14">
-        <v>4520.0</v>
-      </c>
-      <c r="D12" s="14">
-        <v>6230.0</v>
-      </c>
-      <c r="E12" s="14">
-        <v>5630.0</v>
-      </c>
-      <c r="F12" s="14">
-        <v>7640.0</v>
-      </c>
-      <c r="G12" s="14">
-        <v>8840.0</v>
-      </c>
-      <c r="H12" s="14">
+      <c r="C12" s="21">
+        <v>8040.0</v>
+      </c>
+      <c r="D12" s="21">
+        <v>8440.0</v>
+      </c>
+      <c r="E12" s="21">
+        <v>10000.0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>10400.0</v>
+      </c>
+      <c r="G12" s="21">
+        <v>12100.0</v>
+      </c>
+      <c r="H12" s="21">
+        <v>16100.0</v>
+      </c>
+      <c r="I12" s="21">
+        <v>18100.0</v>
+      </c>
+      <c r="J12" s="21">
+        <v>20900.0</v>
+      </c>
+      <c r="K12" s="21">
+        <v>24500.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="23">
+        <v>28.9</v>
+      </c>
+      <c r="C13" s="24">
         <v>11600.0</v>
       </c>
-      <c r="I12" s="14">
-        <v>13100.0</v>
-      </c>
-      <c r="J12" s="14">
-        <v>16700.0</v>
-      </c>
-      <c r="K12" s="14">
-        <v>19500.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="16">
-        <v>28.9</v>
-      </c>
-      <c r="C13" s="17">
-        <v>6500.0</v>
-      </c>
-      <c r="D13" s="17">
-        <v>8960.0</v>
-      </c>
-      <c r="E13" s="17">
-        <v>8090.0</v>
-      </c>
-      <c r="F13" s="17">
-        <v>11000.0</v>
-      </c>
-      <c r="G13" s="17">
-        <v>12700.0</v>
-      </c>
-      <c r="H13" s="17">
-        <v>16800.0</v>
-      </c>
-      <c r="I13" s="17">
-        <v>18800.0</v>
-      </c>
-      <c r="J13" s="17">
-        <v>24000.0</v>
-      </c>
-      <c r="K13" s="17">
-        <v>28000.0</v>
+      <c r="D13" s="24">
+        <v>12100.0</v>
+      </c>
+      <c r="E13" s="24">
+        <v>14400.0</v>
+      </c>
+      <c r="F13" s="24">
+        <v>15000.0</v>
+      </c>
+      <c r="G13" s="24">
+        <v>17300.0</v>
+      </c>
+      <c r="H13" s="24">
+        <v>23100.0</v>
+      </c>
+      <c r="I13" s="24">
+        <v>26000.0</v>
+      </c>
+      <c r="J13" s="24">
+        <v>30100.0</v>
+      </c>
+      <c r="K13" s="24">
+        <v>35300.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="17">
         <v>36.6</v>
       </c>
-      <c r="C14" s="14">
-        <v>8240.0</v>
-      </c>
-      <c r="D14" s="14">
-        <v>11400.0</v>
-      </c>
-      <c r="E14" s="14">
-        <v>10200.0</v>
-      </c>
-      <c r="F14" s="14">
-        <v>13900.0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>16100.0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>21200.0</v>
-      </c>
-      <c r="I14" s="14">
-        <v>23800.0</v>
-      </c>
-      <c r="J14" s="14">
-        <v>30400.0</v>
-      </c>
-      <c r="K14" s="14">
-        <v>35500.0</v>
+      <c r="C14" s="21">
+        <v>14600.0</v>
+      </c>
+      <c r="D14" s="21">
+        <v>15400.0</v>
+      </c>
+      <c r="E14" s="21">
+        <v>18300.0</v>
+      </c>
+      <c r="F14" s="21">
+        <v>19000.0</v>
+      </c>
+      <c r="G14" s="21">
+        <v>22000.0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>29200.0</v>
+      </c>
+      <c r="I14" s="21">
+        <v>32900.0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>38100.0</v>
+      </c>
+      <c r="K14" s="21">
+        <v>44600.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="16">
+      <c r="A15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="23">
         <v>58.0</v>
       </c>
-      <c r="C15" s="17">
-        <v>13000.0</v>
-      </c>
-      <c r="D15" s="17">
-        <v>18000.0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>16200.0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>22000.0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>25500.0</v>
-      </c>
-      <c r="H15" s="17">
+      <c r="C15" s="24">
+        <v>23200.0</v>
+      </c>
+      <c r="D15" s="24">
+        <v>24400.0</v>
+      </c>
+      <c r="E15" s="24">
+        <v>29000.0</v>
+      </c>
+      <c r="F15" s="24">
+        <v>30200.0</v>
+      </c>
+      <c r="G15" s="24">
+        <v>34800.0</v>
+      </c>
+      <c r="H15" s="24">
+        <v>46400.0</v>
+      </c>
+      <c r="I15" s="24">
+        <v>52200.0</v>
+      </c>
+      <c r="J15" s="24">
+        <v>60300.0</v>
+      </c>
+      <c r="K15" s="24">
+        <v>70800.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="17">
+        <v>84.3</v>
+      </c>
+      <c r="C16" s="21">
         <v>33700.0</v>
       </c>
-      <c r="I15" s="17">
-        <v>37700.0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>48100.0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>56300.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="12">
-        <v>84.3</v>
-      </c>
-      <c r="C16" s="14">
-        <v>19000.0</v>
-      </c>
-      <c r="D16" s="14">
-        <v>26100.0</v>
-      </c>
-      <c r="E16" s="14">
-        <v>23600.0</v>
-      </c>
-      <c r="F16" s="14">
-        <v>32000.0</v>
-      </c>
-      <c r="G16" s="14">
-        <v>37100.0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>48900.0</v>
-      </c>
-      <c r="I16" s="14">
-        <v>54800.0</v>
-      </c>
-      <c r="J16" s="14">
-        <v>70000.0</v>
-      </c>
-      <c r="K16" s="14">
-        <v>81800.0</v>
+      <c r="D16" s="21">
+        <v>35400.0</v>
+      </c>
+      <c r="E16" s="21">
+        <v>42200.0</v>
+      </c>
+      <c r="F16" s="21">
+        <v>43800.0</v>
+      </c>
+      <c r="G16" s="21">
+        <v>50600.0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>67400.0</v>
+      </c>
+      <c r="I16" s="21">
+        <v>75900.0</v>
+      </c>
+      <c r="J16" s="21">
+        <v>87700.0</v>
+      </c>
+      <c r="K16" s="21">
+        <v>103000.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="16">
+      <c r="A17" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="23">
         <v>115.0</v>
       </c>
-      <c r="C17" s="17">
-        <v>25900.0</v>
-      </c>
-      <c r="D17" s="17">
-        <v>35600.0</v>
-      </c>
-      <c r="E17" s="17">
-        <v>32200.0</v>
-      </c>
-      <c r="F17" s="17">
-        <v>43700.0</v>
-      </c>
-      <c r="G17" s="17">
-        <v>50600.0</v>
-      </c>
-      <c r="H17" s="17">
-        <v>66700.0</v>
-      </c>
-      <c r="I17" s="17">
-        <v>74800.0</v>
-      </c>
-      <c r="J17" s="17">
-        <v>95500.0</v>
-      </c>
-      <c r="K17" s="17">
-        <v>112000.0</v>
+      <c r="C17" s="24">
+        <v>46000.0</v>
+      </c>
+      <c r="D17" s="24">
+        <v>48300.0</v>
+      </c>
+      <c r="E17" s="24">
+        <v>57500.0</v>
+      </c>
+      <c r="F17" s="24">
+        <v>59800.0</v>
+      </c>
+      <c r="G17" s="24">
+        <v>69000.0</v>
+      </c>
+      <c r="H17" s="24">
+        <v>92000.0</v>
+      </c>
+      <c r="I17" s="24">
+        <v>104000.0</v>
+      </c>
+      <c r="J17" s="24">
+        <v>120000.0</v>
+      </c>
+      <c r="K17" s="24">
+        <v>140000.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="17">
         <v>157.0</v>
       </c>
-      <c r="C18" s="14">
-        <v>35300.0</v>
-      </c>
-      <c r="D18" s="14">
-        <v>48700.0</v>
-      </c>
-      <c r="E18" s="14">
-        <v>44000.0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>59700.0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>69100.0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>91000.0</v>
-      </c>
-      <c r="I18" s="14">
-        <v>102000.0</v>
-      </c>
-      <c r="J18" s="14">
-        <v>130000.0</v>
-      </c>
-      <c r="K18" s="14">
+      <c r="C18" s="21">
+        <v>62800.0</v>
+      </c>
+      <c r="D18" s="21">
+        <v>65900.0</v>
+      </c>
+      <c r="E18" s="21">
+        <v>78500.0</v>
+      </c>
+      <c r="F18" s="21">
+        <v>81600.0</v>
+      </c>
+      <c r="G18" s="21">
+        <v>94000.0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>125000.0</v>
+      </c>
+      <c r="I18" s="21">
+        <v>141000.0</v>
+      </c>
+      <c r="J18" s="21">
+        <v>163000.0</v>
+      </c>
+      <c r="K18" s="21">
+        <v>192000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="23">
+        <v>192.0</v>
+      </c>
+      <c r="C19" s="24">
+        <v>76800.0</v>
+      </c>
+      <c r="D19" s="24">
+        <v>80600.0</v>
+      </c>
+      <c r="E19" s="24">
+        <v>96000.0</v>
+      </c>
+      <c r="F19" s="24">
+        <v>99800.0</v>
+      </c>
+      <c r="G19" s="24">
+        <v>115000.0</v>
+      </c>
+      <c r="H19" s="24">
+        <v>159000.0</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="24">
+        <v>200000.0</v>
+      </c>
+      <c r="K19" s="24">
+        <v>234000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="17">
+        <v>245.0</v>
+      </c>
+      <c r="C20" s="21">
+        <v>98000.0</v>
+      </c>
+      <c r="D20" s="21">
+        <v>103000.0</v>
+      </c>
+      <c r="E20" s="21">
+        <v>122000.0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>127000.0</v>
+      </c>
+      <c r="G20" s="21">
+        <v>147000.0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>203000.0</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="21">
+        <v>255000.0</v>
+      </c>
+      <c r="K20" s="21">
+        <v>299000.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="23">
+        <v>303.0</v>
+      </c>
+      <c r="C21" s="24">
+        <v>121000.0</v>
+      </c>
+      <c r="D21" s="24">
+        <v>127000.0</v>
+      </c>
+      <c r="E21" s="24">
         <v>152000.0</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="16">
-        <v>192.0</v>
-      </c>
-      <c r="C19" s="17">
-        <v>43200.0</v>
-      </c>
-      <c r="D19" s="17">
-        <v>59500.0</v>
-      </c>
-      <c r="E19" s="17">
-        <v>53800.0</v>
-      </c>
-      <c r="F19" s="17">
-        <v>73000.0</v>
-      </c>
-      <c r="G19" s="17">
-        <v>84500.0</v>
-      </c>
-      <c r="H19" s="17">
-        <v>115000.0</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="17">
-        <v>159000.0</v>
-      </c>
-      <c r="K19" s="17">
-        <v>186000.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="12">
-        <v>245.0</v>
-      </c>
-      <c r="C20" s="14">
-        <v>55100.0</v>
-      </c>
-      <c r="D20" s="14">
-        <v>76000.0</v>
-      </c>
-      <c r="E20" s="14">
-        <v>68600.0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>93100.0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>108000.0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>147000.0</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="14">
-        <v>203000.0</v>
-      </c>
-      <c r="K20" s="14">
-        <v>238000.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="16">
-        <v>303.0</v>
-      </c>
-      <c r="C21" s="17">
-        <v>68200.0</v>
-      </c>
-      <c r="D21" s="17">
-        <v>93900.0</v>
-      </c>
-      <c r="E21" s="17">
-        <v>84800.0</v>
-      </c>
-      <c r="F21" s="17">
-        <v>115000.0</v>
-      </c>
-      <c r="G21" s="17">
-        <v>133000.0</v>
-      </c>
-      <c r="H21" s="17">
+      <c r="F21" s="24">
+        <v>158000.0</v>
+      </c>
+      <c r="G21" s="24">
         <v>182000.0</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="17">
+      <c r="H21" s="24">
         <v>252000.0</v>
       </c>
-      <c r="K21" s="17">
-        <v>294000.0</v>
+      <c r="I21" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="24">
+        <v>315000.0</v>
+      </c>
+      <c r="K21" s="24">
+        <v>370000.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="12">
+      <c r="A22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="17">
         <v>353.0</v>
       </c>
-      <c r="C22" s="14">
-        <v>79400.0</v>
-      </c>
-      <c r="D22" s="14">
-        <v>109000.0</v>
-      </c>
-      <c r="E22" s="14">
-        <v>98800.0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>134000.0</v>
-      </c>
-      <c r="G22" s="14">
-        <v>155000.0</v>
-      </c>
-      <c r="H22" s="14">
+      <c r="C22" s="21">
+        <v>141000.0</v>
+      </c>
+      <c r="D22" s="21">
+        <v>148000.0</v>
+      </c>
+      <c r="E22" s="21">
+        <v>176000.0</v>
+      </c>
+      <c r="F22" s="21">
+        <v>184000.0</v>
+      </c>
+      <c r="G22" s="21">
         <v>212000.0</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="H22" s="21">
         <v>293000.0</v>
       </c>
-      <c r="K22" s="14">
-        <v>342000.0</v>
+      <c r="I22" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="21">
+        <v>367000.0</v>
+      </c>
+      <c r="K22" s="21">
+        <v>431000.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="16">
+      <c r="A23" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="23">
         <v>459.0</v>
       </c>
-      <c r="C23" s="17">
-        <v>103000.0</v>
-      </c>
-      <c r="D23" s="17">
-        <v>142000.0</v>
-      </c>
-      <c r="E23" s="17">
-        <v>128000.0</v>
-      </c>
-      <c r="F23" s="17">
-        <v>174000.0</v>
-      </c>
-      <c r="G23" s="17">
-        <v>202000.0</v>
-      </c>
-      <c r="H23" s="17">
+      <c r="C23" s="24">
+        <v>184000.0</v>
+      </c>
+      <c r="D23" s="24">
+        <v>193000.0</v>
+      </c>
+      <c r="E23" s="24">
+        <v>230000.0</v>
+      </c>
+      <c r="F23" s="24">
+        <v>239000.0</v>
+      </c>
+      <c r="G23" s="24">
         <v>275000.0</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="17">
+      <c r="H23" s="24">
         <v>381000.0</v>
       </c>
-      <c r="K23" s="17">
-        <v>445000.0</v>
+      <c r="I23" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="24">
+        <v>477000.0</v>
+      </c>
+      <c r="K23" s="24">
+        <v>560000.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="12">
+      <c r="A24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="17">
         <v>561.0</v>
       </c>
-      <c r="C24" s="14">
-        <v>126000.0</v>
-      </c>
-      <c r="D24" s="14">
-        <v>174000.0</v>
-      </c>
-      <c r="E24" s="14">
-        <v>157000.0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>213000.0</v>
-      </c>
-      <c r="G24" s="14">
-        <v>247000.0</v>
-      </c>
-      <c r="H24" s="14">
+      <c r="C24" s="21">
+        <v>224000.0</v>
+      </c>
+      <c r="D24" s="21">
+        <v>236000.0</v>
+      </c>
+      <c r="E24" s="21">
+        <v>280000.0</v>
+      </c>
+      <c r="F24" s="21">
+        <v>292000.0</v>
+      </c>
+      <c r="G24" s="21">
         <v>337000.0</v>
       </c>
-      <c r="I24" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="14">
+      <c r="H24" s="21">
         <v>466000.0</v>
       </c>
-      <c r="K24" s="14">
-        <v>544000.0</v>
+      <c r="I24" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="21">
+        <v>583000.0</v>
+      </c>
+      <c r="K24" s="21">
+        <v>684000.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="16">
+      <c r="A25" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="23">
         <v>694.0</v>
       </c>
-      <c r="C25" s="17">
-        <v>156000.0</v>
-      </c>
-      <c r="D25" s="17">
-        <v>215000.0</v>
-      </c>
-      <c r="E25" s="17">
-        <v>194000.0</v>
-      </c>
-      <c r="F25" s="17">
-        <v>264000.0</v>
-      </c>
-      <c r="G25" s="17">
-        <v>305000.0</v>
-      </c>
-      <c r="H25" s="17">
+      <c r="C25" s="24">
+        <v>278000.0</v>
+      </c>
+      <c r="D25" s="24">
+        <v>292000.0</v>
+      </c>
+      <c r="E25" s="24">
+        <v>347000.0</v>
+      </c>
+      <c r="F25" s="24">
+        <v>361000.0</v>
+      </c>
+      <c r="G25" s="24">
         <v>416000.0</v>
       </c>
-      <c r="I25" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="17">
+      <c r="H25" s="24">
         <v>576000.0</v>
       </c>
-      <c r="K25" s="17">
-        <v>673000.0</v>
+      <c r="I25" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="24">
+        <v>722000.0</v>
+      </c>
+      <c r="K25" s="24">
+        <v>847000.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="17">
         <v>817.0</v>
       </c>
-      <c r="C26" s="14">
-        <v>184000.0</v>
-      </c>
-      <c r="D26" s="14">
-        <v>253000.0</v>
-      </c>
-      <c r="E26" s="14">
-        <v>229000.0</v>
-      </c>
-      <c r="F26" s="14">
-        <v>310000.0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>359000.0</v>
-      </c>
-      <c r="H26" s="14">
+      <c r="C26" s="21">
+        <v>327000.0</v>
+      </c>
+      <c r="D26" s="21">
+        <v>343000.0</v>
+      </c>
+      <c r="E26" s="21">
+        <v>408000.0</v>
+      </c>
+      <c r="F26" s="21">
+        <v>425000.0</v>
+      </c>
+      <c r="G26" s="21">
         <v>490000.0</v>
       </c>
-      <c r="I26" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" s="14">
+      <c r="H26" s="21">
         <v>678000.0</v>
       </c>
-      <c r="K26" s="14">
-        <v>792000.0</v>
+      <c r="I26" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="21">
+        <v>850000.0</v>
+      </c>
+      <c r="K26" s="21">
+        <v>997000.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="16">
+      <c r="A27" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="23">
         <v>976.0</v>
       </c>
-      <c r="C27" s="17">
-        <v>220000.0</v>
-      </c>
-      <c r="D27" s="17">
-        <v>303000.0</v>
-      </c>
-      <c r="E27" s="17">
-        <v>273000.0</v>
-      </c>
-      <c r="F27" s="17">
-        <v>371000.0</v>
-      </c>
-      <c r="G27" s="17">
-        <v>429000.0</v>
-      </c>
-      <c r="H27" s="17">
+      <c r="C27" s="24">
+        <v>390000.0</v>
+      </c>
+      <c r="D27" s="24">
+        <v>410000.0</v>
+      </c>
+      <c r="E27" s="24">
+        <v>488000.0</v>
+      </c>
+      <c r="F27" s="24">
+        <v>508000.0</v>
+      </c>
+      <c r="G27" s="24">
         <v>586000.0</v>
       </c>
-      <c r="I27" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="17">
+      <c r="H27" s="24">
         <v>810000.0</v>
       </c>
-      <c r="K27" s="17">
-        <v>947000.0</v>
+      <c r="I27" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="24">
+        <v>1020000.0</v>
+      </c>
+      <c r="K27" s="24">
+        <v>1200000.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>54</v>
+      <c r="A30" s="30" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>58</v>
+      <c r="A31" s="31" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="20" t="s">
-        <v>59</v>
+      <c r="A32" s="31" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="33" ht="21.75" customHeight="1">
-      <c r="A33" s="20" t="s">
-        <v>60</v>
+      <c r="A33" s="31" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="20" t="s">
-        <v>62</v>
+      <c r="A34" s="31" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -4433,12 +5329,1804 @@
     <col customWidth="1" min="1" max="1" width="12.0"/>
     <col customWidth="1" min="2" max="2" width="14.0"/>
     <col customWidth="1" min="3" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" ht="30.0" customHeight="1">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="17">
+        <v>5.03</v>
+      </c>
+      <c r="C8" s="21">
+        <v>1130.0</v>
+      </c>
+      <c r="D8" s="21">
+        <v>1560.0</v>
+      </c>
+      <c r="E8" s="21">
+        <v>1410.0</v>
+      </c>
+      <c r="F8" s="21">
+        <v>1910.0</v>
+      </c>
+      <c r="G8" s="21">
+        <v>2210.0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>2920.0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>3270.0</v>
+      </c>
+      <c r="J8" s="21">
+        <v>4180.0</v>
+      </c>
+      <c r="K8" s="21">
+        <v>4880.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="23">
+        <v>6.78</v>
+      </c>
+      <c r="C9" s="24">
+        <v>1530.0</v>
+      </c>
+      <c r="D9" s="24">
+        <v>2100.0</v>
+      </c>
+      <c r="E9" s="24">
+        <v>1900.0</v>
+      </c>
+      <c r="F9" s="24">
+        <v>2580.0</v>
+      </c>
+      <c r="G9" s="24">
+        <v>2980.0</v>
+      </c>
+      <c r="H9" s="24">
+        <v>3940.0</v>
+      </c>
+      <c r="I9" s="24">
+        <v>4410.0</v>
+      </c>
+      <c r="J9" s="24">
+        <v>5630.0</v>
+      </c>
+      <c r="K9" s="24">
+        <v>6580.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="17">
+        <v>8.78</v>
+      </c>
+      <c r="C10" s="21">
+        <v>1980.0</v>
+      </c>
+      <c r="D10" s="21">
+        <v>2720.0</v>
+      </c>
+      <c r="E10" s="21">
+        <v>2460.0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>3340.0</v>
+      </c>
+      <c r="G10" s="21">
+        <v>3860.0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>5100.0</v>
+      </c>
+      <c r="I10" s="21">
+        <v>5710.0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>7290.0</v>
+      </c>
+      <c r="K10" s="21">
+        <v>8520.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="23">
+        <v>14.2</v>
+      </c>
+      <c r="C11" s="24">
+        <v>3200.0</v>
+      </c>
+      <c r="D11" s="24">
+        <v>4400.0</v>
+      </c>
+      <c r="E11" s="24">
+        <v>3980.0</v>
+      </c>
+      <c r="F11" s="24">
+        <v>5400.0</v>
+      </c>
+      <c r="G11" s="24">
+        <v>6250.0</v>
+      </c>
+      <c r="H11" s="24">
+        <v>8230.0</v>
+      </c>
+      <c r="I11" s="24">
+        <v>9230.0</v>
+      </c>
+      <c r="J11" s="24">
+        <v>11800.0</v>
+      </c>
+      <c r="K11" s="24">
+        <v>13800.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="17">
+        <v>20.1</v>
+      </c>
+      <c r="C12" s="21">
+        <v>4520.0</v>
+      </c>
+      <c r="D12" s="21">
+        <v>6230.0</v>
+      </c>
+      <c r="E12" s="21">
+        <v>5630.0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>7640.0</v>
+      </c>
+      <c r="G12" s="21">
+        <v>8840.0</v>
+      </c>
+      <c r="H12" s="21">
+        <v>11600.0</v>
+      </c>
+      <c r="I12" s="21">
+        <v>13100.0</v>
+      </c>
+      <c r="J12" s="21">
+        <v>16700.0</v>
+      </c>
+      <c r="K12" s="21">
+        <v>19500.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="23">
+        <v>28.9</v>
+      </c>
+      <c r="C13" s="24">
+        <v>6500.0</v>
+      </c>
+      <c r="D13" s="24">
+        <v>8960.0</v>
+      </c>
+      <c r="E13" s="24">
+        <v>8090.0</v>
+      </c>
+      <c r="F13" s="24">
+        <v>11000.0</v>
+      </c>
+      <c r="G13" s="24">
+        <v>12700.0</v>
+      </c>
+      <c r="H13" s="24">
+        <v>16800.0</v>
+      </c>
+      <c r="I13" s="24">
+        <v>18800.0</v>
+      </c>
+      <c r="J13" s="24">
+        <v>24000.0</v>
+      </c>
+      <c r="K13" s="24">
+        <v>28000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="17">
+        <v>36.6</v>
+      </c>
+      <c r="C14" s="21">
+        <v>8240.0</v>
+      </c>
+      <c r="D14" s="21">
+        <v>11400.0</v>
+      </c>
+      <c r="E14" s="21">
+        <v>10200.0</v>
+      </c>
+      <c r="F14" s="21">
+        <v>13900.0</v>
+      </c>
+      <c r="G14" s="21">
+        <v>16100.0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>21200.0</v>
+      </c>
+      <c r="I14" s="21">
+        <v>23800.0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>30400.0</v>
+      </c>
+      <c r="K14" s="21">
+        <v>35500.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="23">
+        <v>58.0</v>
+      </c>
+      <c r="C15" s="24">
+        <v>13000.0</v>
+      </c>
+      <c r="D15" s="24">
+        <v>18000.0</v>
+      </c>
+      <c r="E15" s="24">
+        <v>16200.0</v>
+      </c>
+      <c r="F15" s="24">
+        <v>22000.0</v>
+      </c>
+      <c r="G15" s="24">
+        <v>25500.0</v>
+      </c>
+      <c r="H15" s="24">
+        <v>33700.0</v>
+      </c>
+      <c r="I15" s="24">
+        <v>37700.0</v>
+      </c>
+      <c r="J15" s="24">
+        <v>48100.0</v>
+      </c>
+      <c r="K15" s="24">
+        <v>56300.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="17">
+        <v>84.3</v>
+      </c>
+      <c r="C16" s="21">
+        <v>19000.0</v>
+      </c>
+      <c r="D16" s="21">
+        <v>26100.0</v>
+      </c>
+      <c r="E16" s="21">
+        <v>23600.0</v>
+      </c>
+      <c r="F16" s="21">
+        <v>32000.0</v>
+      </c>
+      <c r="G16" s="21">
+        <v>37100.0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>48900.0</v>
+      </c>
+      <c r="I16" s="21">
+        <v>54800.0</v>
+      </c>
+      <c r="J16" s="21">
+        <v>70000.0</v>
+      </c>
+      <c r="K16" s="21">
+        <v>81800.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="23">
+        <v>115.0</v>
+      </c>
+      <c r="C17" s="24">
+        <v>25900.0</v>
+      </c>
+      <c r="D17" s="24">
+        <v>35600.0</v>
+      </c>
+      <c r="E17" s="24">
+        <v>32200.0</v>
+      </c>
+      <c r="F17" s="24">
+        <v>43700.0</v>
+      </c>
+      <c r="G17" s="24">
+        <v>50600.0</v>
+      </c>
+      <c r="H17" s="24">
+        <v>66700.0</v>
+      </c>
+      <c r="I17" s="24">
+        <v>74800.0</v>
+      </c>
+      <c r="J17" s="24">
+        <v>95500.0</v>
+      </c>
+      <c r="K17" s="24">
+        <v>112000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="17">
+        <v>157.0</v>
+      </c>
+      <c r="C18" s="21">
+        <v>35300.0</v>
+      </c>
+      <c r="D18" s="21">
+        <v>48700.0</v>
+      </c>
+      <c r="E18" s="21">
+        <v>44000.0</v>
+      </c>
+      <c r="F18" s="21">
+        <v>59700.0</v>
+      </c>
+      <c r="G18" s="21">
+        <v>69100.0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>91000.0</v>
+      </c>
+      <c r="I18" s="21">
+        <v>102000.0</v>
+      </c>
+      <c r="J18" s="21">
+        <v>130000.0</v>
+      </c>
+      <c r="K18" s="21">
+        <v>152000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="23">
+        <v>192.0</v>
+      </c>
+      <c r="C19" s="24">
+        <v>43200.0</v>
+      </c>
+      <c r="D19" s="24">
+        <v>59500.0</v>
+      </c>
+      <c r="E19" s="24">
+        <v>53800.0</v>
+      </c>
+      <c r="F19" s="24">
+        <v>73000.0</v>
+      </c>
+      <c r="G19" s="24">
+        <v>84500.0</v>
+      </c>
+      <c r="H19" s="24">
+        <v>115000.0</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="24">
+        <v>159000.0</v>
+      </c>
+      <c r="K19" s="24">
+        <v>186000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="17">
+        <v>245.0</v>
+      </c>
+      <c r="C20" s="21">
+        <v>55100.0</v>
+      </c>
+      <c r="D20" s="21">
+        <v>76000.0</v>
+      </c>
+      <c r="E20" s="21">
+        <v>68600.0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>93100.0</v>
+      </c>
+      <c r="G20" s="21">
+        <v>108000.0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>147000.0</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="21">
+        <v>203000.0</v>
+      </c>
+      <c r="K20" s="21">
+        <v>238000.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="23">
+        <v>303.0</v>
+      </c>
+      <c r="C21" s="24">
+        <v>68200.0</v>
+      </c>
+      <c r="D21" s="24">
+        <v>93900.0</v>
+      </c>
+      <c r="E21" s="24">
+        <v>84800.0</v>
+      </c>
+      <c r="F21" s="24">
+        <v>115000.0</v>
+      </c>
+      <c r="G21" s="24">
+        <v>133000.0</v>
+      </c>
+      <c r="H21" s="24">
+        <v>182000.0</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="24">
+        <v>252000.0</v>
+      </c>
+      <c r="K21" s="24">
+        <v>294000.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="17">
+        <v>353.0</v>
+      </c>
+      <c r="C22" s="21">
+        <v>79400.0</v>
+      </c>
+      <c r="D22" s="21">
+        <v>109000.0</v>
+      </c>
+      <c r="E22" s="21">
+        <v>98800.0</v>
+      </c>
+      <c r="F22" s="21">
+        <v>134000.0</v>
+      </c>
+      <c r="G22" s="21">
+        <v>155000.0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>212000.0</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="21">
+        <v>293000.0</v>
+      </c>
+      <c r="K22" s="21">
+        <v>342000.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="23">
+        <v>459.0</v>
+      </c>
+      <c r="C23" s="24">
+        <v>103000.0</v>
+      </c>
+      <c r="D23" s="24">
+        <v>142000.0</v>
+      </c>
+      <c r="E23" s="24">
+        <v>128000.0</v>
+      </c>
+      <c r="F23" s="24">
+        <v>174000.0</v>
+      </c>
+      <c r="G23" s="24">
+        <v>202000.0</v>
+      </c>
+      <c r="H23" s="24">
+        <v>275000.0</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="24">
+        <v>381000.0</v>
+      </c>
+      <c r="K23" s="24">
+        <v>445000.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="17">
+        <v>561.0</v>
+      </c>
+      <c r="C24" s="21">
+        <v>126000.0</v>
+      </c>
+      <c r="D24" s="21">
+        <v>174000.0</v>
+      </c>
+      <c r="E24" s="21">
+        <v>157000.0</v>
+      </c>
+      <c r="F24" s="21">
+        <v>213000.0</v>
+      </c>
+      <c r="G24" s="21">
+        <v>247000.0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>337000.0</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="21">
+        <v>466000.0</v>
+      </c>
+      <c r="K24" s="21">
+        <v>544000.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="23">
+        <v>694.0</v>
+      </c>
+      <c r="C25" s="24">
+        <v>156000.0</v>
+      </c>
+      <c r="D25" s="24">
+        <v>215000.0</v>
+      </c>
+      <c r="E25" s="24">
+        <v>194000.0</v>
+      </c>
+      <c r="F25" s="24">
+        <v>264000.0</v>
+      </c>
+      <c r="G25" s="24">
+        <v>305000.0</v>
+      </c>
+      <c r="H25" s="24">
+        <v>416000.0</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="24">
+        <v>576000.0</v>
+      </c>
+      <c r="K25" s="24">
+        <v>673000.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="17">
+        <v>817.0</v>
+      </c>
+      <c r="C26" s="21">
+        <v>184000.0</v>
+      </c>
+      <c r="D26" s="21">
+        <v>253000.0</v>
+      </c>
+      <c r="E26" s="21">
+        <v>229000.0</v>
+      </c>
+      <c r="F26" s="21">
+        <v>310000.0</v>
+      </c>
+      <c r="G26" s="21">
+        <v>359000.0</v>
+      </c>
+      <c r="H26" s="21">
+        <v>490000.0</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="21">
+        <v>678000.0</v>
+      </c>
+      <c r="K26" s="21">
+        <v>792000.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="23">
+        <v>976.0</v>
+      </c>
+      <c r="C27" s="24">
+        <v>220000.0</v>
+      </c>
+      <c r="D27" s="24">
+        <v>303000.0</v>
+      </c>
+      <c r="E27" s="24">
+        <v>273000.0</v>
+      </c>
+      <c r="F27" s="24">
+        <v>371000.0</v>
+      </c>
+      <c r="G27" s="24">
+        <v>429000.0</v>
+      </c>
+      <c r="H27" s="24">
+        <v>586000.0</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="24">
+        <v>810000.0</v>
+      </c>
+      <c r="K27" s="24">
+        <v>947000.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" ht="15.0" customHeight="1">
+      <c r="A31" s="31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" ht="15.0" customHeight="1">
+      <c r="A32" s="31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" ht="21.75" customHeight="1">
+      <c r="A33" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="A34" s="31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="A7:K7"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="14.0"/>
+    <col customWidth="1" min="3" max="11" width="12.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -4454,624 +7142,624 @@
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="D6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="E6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="F6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="G6" s="14" t="s">
         <v>16</v>
       </c>
+      <c r="H6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>17</v>
+      <c r="A7" s="15" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="17">
         <v>39.2</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="21">
         <v>15700.0</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="21">
         <v>16500.0</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="21">
         <v>19600.0</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="21">
         <v>20400.0</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="21">
         <v>23500.0</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="21">
         <v>31360.0</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="21">
         <v>35300.0</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="21">
         <v>40800.0</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="21">
         <v>47800.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="23">
         <v>61.2</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="24">
         <v>24500.0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="24">
         <v>25700.0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="24">
         <v>30600.0</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="24">
         <v>31800.0</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="24">
         <v>36700.0</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="24">
         <v>49000.0</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="24">
         <v>55100.0</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="24">
         <v>63600.0</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="24">
         <v>74700.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="17">
         <v>64.5</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="21">
         <v>25800.0</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="21">
         <v>27100.0</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="21">
         <v>32300.0</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="21">
         <v>33500.0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="21">
         <v>38700.0</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="21">
         <v>51600.0</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="21">
         <v>58100.0</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="21">
         <v>67100.0</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="21">
         <v>78700.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="23">
         <v>88.1</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="24">
         <v>35200.0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="24">
         <v>37000.0</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="24">
         <v>44100.0</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="24">
         <v>45800.0</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="24">
         <v>52900.0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="24">
         <v>70500.0</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="24">
         <v>79300.0</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="24">
         <v>91600.0</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="24">
         <v>107000.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="17">
         <v>92.1</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="21">
         <v>36800.0</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="21">
         <v>38700.0</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="21">
         <v>46100.0</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="21">
         <v>47900.0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="21">
         <v>55300.0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="21">
         <v>73700.0</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="21">
         <v>82900.0</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="21">
         <v>95800.0</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="21">
         <v>112000.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="16">
+      <c r="A13" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="23">
         <v>125.0</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="24">
         <v>50000.0</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="24">
         <v>52500.0</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="24">
         <v>62500.0</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="24">
         <v>65000.0</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="24">
         <v>75000.0</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="24">
         <v>100000.0</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="24">
         <v>112000.0</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="24">
         <v>130000.0</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="24">
         <v>152000.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="17">
         <v>167.0</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="21">
         <v>66800.0</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="21">
         <v>70100.0</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="21">
         <v>83500.0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="21">
         <v>86800.0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="21">
         <v>100000.0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="21">
         <v>134000.0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="21">
         <v>150000.0</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="21">
         <v>174000.0</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="21">
         <v>204000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="16">
+      <c r="A15" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="23">
         <v>216.0</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="24">
         <v>86400.0</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="24">
         <v>90700.0</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="24">
         <v>108000.0</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="24">
         <v>112000.0</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="24">
         <v>130000.0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="24">
         <v>179000.0</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="17">
+      <c r="I15" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="24">
         <v>225000.0</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="24">
         <v>264000.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="17">
         <v>272.0</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="21">
         <v>109000.0</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="21">
         <v>114000.0</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="21">
         <v>136000.0</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="21">
         <v>141000.0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="21">
         <v>163000.0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="21">
         <v>226000.0</v>
       </c>
-      <c r="I16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="14">
+      <c r="I16" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="21">
         <v>283000.0</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="21">
         <v>332000.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="16">
+      <c r="A17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="23">
         <v>333.0</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="24">
         <v>133000.0</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="24">
         <v>140000.0</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="24">
         <v>166000.0</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="24">
         <v>173000.0</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="24">
         <v>200000.0</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="24">
         <v>276000.0</v>
       </c>
-      <c r="I17" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="17">
+      <c r="I17" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="24">
         <v>346000.0</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="24">
         <v>406000.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="17">
         <v>384.0</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="21">
         <v>154000.0</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="21">
         <v>161000.0</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="21">
         <v>192000.0</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="21">
         <v>200000.0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="21">
         <v>230000.0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="21">
         <v>319000.0</v>
       </c>
-      <c r="I18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="I18" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="21">
         <v>399000.0</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="21">
         <v>469000.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="16">
+      <c r="A19" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="23">
         <v>496.0</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="24">
         <v>198000.0</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="24">
         <v>208000.0</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="24">
         <v>248000.0</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="24">
         <v>258000.0</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="24">
         <v>298000.0</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="24">
         <v>412000.0</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="17">
+      <c r="I19" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="24">
         <v>516000.0</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="24">
         <v>605000.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="A20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="17">
         <v>621.0</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="21">
         <v>248000.0</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="21">
         <v>261000.0</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="21">
         <v>310000.0</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="21">
         <v>323000.0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="21">
         <v>373000.0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="21">
         <v>515000.0</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="14">
+      <c r="I20" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="21">
         <v>646000.0</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="21">
         <v>758000.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="16">
+      <c r="A21" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="23">
         <v>761.0</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="24">
         <v>304000.0</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="24">
         <v>320000.0</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="24">
         <v>380000.0</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="24">
         <v>396000.0</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="24">
         <v>457000.0</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="24">
         <v>632000.0</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="17">
+      <c r="I21" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="24">
         <v>791000.0</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="24">
         <v>928000.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="12">
+      <c r="A22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="17">
         <v>865.0</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="21">
         <v>346000.0</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="21">
         <v>363000.0</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="21">
         <v>432000.0</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="21">
         <v>450000.0</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="21">
         <v>519000.0</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="21">
         <v>718000.0</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="I22" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="21">
         <v>900000.0</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="21">
         <v>1055000.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="16">
+      <c r="A23" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="23">
         <v>1030.0</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="24">
         <v>412000.0</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="24">
         <v>433000.0</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="24">
         <v>515000.0</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="24">
         <v>536000.0</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="24">
         <v>618000.0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="24">
         <v>855000.0</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="17">
+      <c r="I23" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="24">
         <v>1070000.0</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="24">
         <v>1260000.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>54</v>
+      <c r="A26" s="30" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>55</v>
+      <c r="A27" s="31" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -6065,7 +8753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -6075,12 +8763,11 @@
     <col customWidth="1" min="1" max="1" width="12.0"/>
     <col customWidth="1" min="2" max="2" width="14.0"/>
     <col customWidth="1" min="3" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2">
@@ -6096,624 +8783,624 @@
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="D6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="E6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="F6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="G6" s="14" t="s">
         <v>16</v>
       </c>
+      <c r="H6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>18</v>
+      <c r="A7" s="15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="17">
         <v>39.2</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="21">
         <v>8820.0</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="21">
         <v>12200.0</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="21">
         <v>11000.0</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="21">
         <v>14900.0</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="21">
         <v>17200.0</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="21">
         <v>22700.0</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="21">
         <v>25500.0</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="21">
         <v>32500.0</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="21">
         <v>38000.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="23">
         <v>61.2</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="24">
         <v>13800.0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="24">
         <v>19000.0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="24">
         <v>17100.0</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="24">
         <v>23300.0</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="24">
         <v>26900.0</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="24">
         <v>35500.0</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="24">
         <v>39800.0</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="24">
         <v>50800.0</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="24">
         <v>59400.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="17">
         <v>64.5</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="21">
         <v>14500.0</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="21">
         <v>20000.0</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="21">
         <v>18100.0</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="21">
         <v>24500.0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="21">
         <v>28400.0</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="21">
         <v>37400.0</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="21">
         <v>41900.0</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="21">
         <v>53500.0</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="21">
         <v>62700.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="23">
         <v>88.1</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="24">
         <v>19800.0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="24">
         <v>27300.0</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="24">
         <v>24700.0</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="24">
         <v>33500.0</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="24">
         <v>38800.0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="24">
         <v>51100.0</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="24">
         <v>57300.0</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="24">
         <v>73100.0</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="24">
         <v>85500.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="17">
         <v>92.1</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="21">
         <v>20700.0</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="21">
         <v>28600.0</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="21">
         <v>25800.0</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="21">
         <v>35000.0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="21">
         <v>40500.0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="21">
         <v>53400.0</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="21">
         <v>59900.0</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="21">
         <v>76400.0</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="21">
         <v>89300.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="16">
+      <c r="A13" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="23">
         <v>125.0</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="24">
         <v>28100.0</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="24">
         <v>38800.0</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="24">
         <v>35000.0</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="24">
         <v>47500.0</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="24">
         <v>55000.0</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="24">
         <v>72500.0</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="24">
         <v>81200.0</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="24">
         <v>104000.0</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="24">
         <v>121000.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="17">
         <v>167.0</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="21">
         <v>37600.0</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="21">
         <v>51800.0</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="21">
         <v>46800.0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="21">
         <v>63500.0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="21">
         <v>73500.0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="21">
         <v>96900.0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="21">
         <v>109000.0</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="21">
         <v>139000.0</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="21">
         <v>162000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="16">
+      <c r="A15" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="23">
         <v>216.0</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="24">
         <v>48600.0</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="24">
         <v>67000.0</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="24">
         <v>60500.0</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="24">
         <v>82100.0</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="24">
         <v>95000.0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="24">
         <v>130000.0</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="17">
+      <c r="I15" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="24">
         <v>179000.0</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="24">
         <v>210000.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="17">
         <v>272.0</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="21">
         <v>61200.0</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="21">
         <v>84300.0</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="21">
         <v>76200.0</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="21">
         <v>103000.0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="21">
         <v>120000.0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="21">
         <v>163000.0</v>
       </c>
-      <c r="I16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="14">
+      <c r="I16" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="21">
         <v>226000.0</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="21">
         <v>264000.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="16">
+      <c r="A17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="23">
         <v>333.0</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="24">
         <v>74900.0</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="24">
         <v>103000.0</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="24">
         <v>93200.0</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="24">
         <v>126000.0</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="24">
         <v>146000.0</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="24">
         <v>200000.0</v>
       </c>
-      <c r="I17" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="17">
+      <c r="I17" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="24">
         <v>276000.0</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="24">
         <v>323000.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="17">
         <v>384.0</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="21">
         <v>86400.0</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="21">
         <v>119000.0</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="21">
         <v>108000.0</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="21">
         <v>146000.0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="21">
         <v>169000.0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="21">
         <v>230000.0</v>
       </c>
-      <c r="I18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="I18" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="21">
         <v>319000.0</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="21">
         <v>372000.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="16">
+      <c r="A19" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="23">
         <v>496.0</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="24">
         <v>112000.0</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="24">
         <v>154000.0</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="24">
         <v>139000.0</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="24">
         <v>188000.0</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="24">
         <v>218000.0</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="24">
         <v>298000.0</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="17">
+      <c r="I19" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="24">
         <v>412000.0</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="24">
         <v>481000.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="A20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="17">
         <v>621.0</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="21">
         <v>140000.0</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="21">
         <v>192000.0</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="21">
         <v>174000.0</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="21">
         <v>236000.0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="21">
         <v>273000.0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="21">
         <v>373000.0</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="14">
+      <c r="I20" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="21">
         <v>515000.0</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="21">
         <v>602000.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="16">
+      <c r="A21" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="23">
         <v>761.0</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="24">
         <v>171000.0</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="24">
         <v>236000.0</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="24">
         <v>213000.0</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="24">
         <v>289000.0</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="24">
         <v>335000.0</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="24">
         <v>457000.0</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="17">
+      <c r="I21" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="24">
         <v>632000.0</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="24">
         <v>738000.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="12">
+      <c r="A22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="17">
         <v>865.0</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="21">
         <v>195000.0</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="21">
         <v>268000.0</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="21">
         <v>242000.0</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="21">
         <v>329000.0</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="21">
         <v>381000.0</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="21">
         <v>519000.0</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="I22" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="21">
         <v>718000.0</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="21">
         <v>839000.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="16">
+      <c r="A23" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="23">
         <v>1030.0</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="24">
         <v>232000.0</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="24">
         <v>319000.0</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="24">
         <v>288000.0</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="24">
         <v>391000.0</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="24">
         <v>453000.0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="24">
         <v>618000.0</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="17">
+      <c r="I23" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="24">
         <v>855000.0</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="24">
         <v>999000.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>54</v>
+      <c r="A26" s="30" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>55</v>
+      <c r="A27" s="31" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
